--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.93877</v>
+        <v>17.11232</v>
       </c>
       <c r="D2" t="n">
-        <v>16.86928</v>
+        <v>16.42804</v>
       </c>
       <c r="E2" t="n">
-        <v>16.47159</v>
+        <v>16.94574</v>
       </c>
       <c r="F2" t="n">
-        <v>42.70988</v>
+        <v>42.27183</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05088</v>
+        <v>0.04976</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78419</v>
+        <v>1.84704</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.85175</v>
+        <v>16.83146</v>
       </c>
       <c r="D3" t="n">
-        <v>16.37316</v>
+        <v>16.55544</v>
       </c>
       <c r="E3" t="n">
-        <v>16.86267</v>
+        <v>16.73679</v>
       </c>
       <c r="F3" t="n">
-        <v>42.3942</v>
+        <v>40.97582</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05037</v>
+        <v>0.05094</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83115</v>
+        <v>1.85261</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.96924</v>
+        <v>16.93301</v>
       </c>
       <c r="D4" t="n">
-        <v>16.69738</v>
+        <v>16.25946</v>
       </c>
       <c r="E4" t="n">
-        <v>16.6162</v>
+        <v>16.74113</v>
       </c>
       <c r="F4" t="n">
-        <v>41.54493</v>
+        <v>42.44039</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05103</v>
+        <v>0.05068</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8067</v>
+        <v>1.8055</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.06245</v>
+        <v>16.85377</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10408</v>
+        <v>15.7163</v>
       </c>
       <c r="E6" t="n">
-        <v>16.33904</v>
+        <v>16.79439</v>
       </c>
       <c r="F6" t="n">
-        <v>21.6885</v>
+        <v>21.72987</v>
       </c>
       <c r="G6" t="n">
-        <v>34.53443</v>
+        <v>34.60813</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.92665</v>
+        <v>16.70431</v>
       </c>
       <c r="D7" t="n">
-        <v>16.19026</v>
+        <v>16.18657</v>
       </c>
       <c r="E7" t="n">
-        <v>16.206</v>
+        <v>16.27624</v>
       </c>
       <c r="F7" t="n">
-        <v>21.7059</v>
+        <v>21.68866</v>
       </c>
       <c r="G7" t="n">
-        <v>34.30704</v>
+        <v>34.23215</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.371</v>
+        <v>16.29271</v>
       </c>
       <c r="D8" t="n">
-        <v>15.57783</v>
+        <v>15.72864</v>
       </c>
       <c r="E8" t="n">
-        <v>16.03836</v>
+        <v>16.20077</v>
       </c>
       <c r="F8" t="n">
-        <v>21.66073</v>
+        <v>21.69249</v>
       </c>
       <c r="G8" t="n">
-        <v>34.60044</v>
+        <v>33.83078</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60033</v>
+        <v>0.60658</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12339</v>
+        <v>1.10361</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60295</v>
+        <v>0.61316</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11349</v>
+        <v>1.1374</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6117899999999999</v>
+        <v>0.59851</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13142</v>
+        <v>1.13065</v>
       </c>
     </row>
   </sheetData>
